--- a/R_Codes/DataSummary/Bacteria/Sample_Type/Bacteria_Summary_Domain_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_Type/Bacteria_Summary_Domain_by_Sample_Type.xlsx
@@ -384,10 +384,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999995</v>
+        <v>99.9999999999994</v>
       </c>
       <c r="D2" t="n">
-        <v>0.189884192435042</v>
+        <v>0.190065819321978</v>
       </c>
     </row>
   </sheetData>
@@ -423,10 +423,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999999</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.268416401793252</v>
+        <v>0.270827818974726</v>
       </c>
     </row>
   </sheetData>
